--- a/Backtest/02-08-21/S&P500stock_02-08-21period252RS90.xlsx
+++ b/Backtest/02-08-21/S&P500stock_02-08-21period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
   <si>
     <t>Stock</t>
   </si>
@@ -127,88 +127,100 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>NUE</t>
-  </si>
-  <si>
-    <t>MRNA</t>
-  </si>
-  <si>
-    <t>STLD</t>
-  </si>
-  <si>
-    <t>COF</t>
-  </si>
-  <si>
-    <t>DFS</t>
-  </si>
-  <si>
-    <t>BX</t>
-  </si>
-  <si>
-    <t>TXT</t>
-  </si>
-  <si>
-    <t>DE</t>
-  </si>
-  <si>
-    <t>HCA</t>
-  </si>
-  <si>
-    <t>GNRC</t>
-  </si>
-  <si>
-    <t>TGT</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>2021-10-21</t>
-  </si>
-  <si>
-    <t>2021-08-05</t>
-  </si>
-  <si>
-    <t>2021-10-18</t>
-  </si>
-  <si>
-    <t>2021-10-26</t>
-  </si>
-  <si>
-    <t>2021-10-20</t>
-  </si>
-  <si>
-    <t>2021-10-28</t>
-  </si>
-  <si>
-    <t>2021-08-20</t>
-  </si>
-  <si>
-    <t>2021-10-22</t>
-  </si>
-  <si>
-    <t>2021-11-02</t>
-  </si>
-  <si>
-    <t>2021-08-18</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
-    <t>2021-10-14</t>
+    <t>PTC</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>PYPL</t>
+  </si>
+  <si>
+    <t>FCX</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>KLAC</t>
+  </si>
+  <si>
+    <t>IDXX</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>SNPS</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>MPWR</t>
+  </si>
+  <si>
+    <t>FSLR</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-05-05</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-05-03</t>
+  </si>
+  <si>
+    <t>2021-04-29</t>
+  </si>
+  <si>
+    <t>2021-05-04</t>
+  </si>
+  <si>
+    <t>2021-02-24</t>
+  </si>
+  <si>
+    <t>2021-02-17</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>2021-02-25</t>
+  </si>
+  <si>
+    <t>2021-05-20</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
   </si>
   <si>
     <t>Basic Materials</t>
@@ -217,55 +229,40 @@
     <t>Healthcare</t>
   </si>
   <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Consumer Defensive</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Steel</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
+    <t>Software - Application</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
   </si>
   <si>
     <t>Credit Services</t>
   </si>
   <si>
-    <t>Asset Management</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>Farm &amp; Heavy Construction Machinery</t>
-  </si>
-  <si>
-    <t>Medical Care Facilities</t>
-  </si>
-  <si>
-    <t>Specialty Industrial Machinery</t>
-  </si>
-  <si>
-    <t>Discount Stores</t>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Internet Retail</t>
   </si>
   <si>
     <t>Semiconductor Equipment &amp; Materials</t>
   </si>
   <si>
-    <t>Information Technology Services</t>
-  </si>
-  <si>
-    <t>Communication Equipment</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
+    <t>Diagnostics &amp; Research</t>
+  </si>
+  <si>
+    <t>Software - Infrastructure</t>
+  </si>
+  <si>
+    <t>Medical Instruments &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
   </si>
 </sst>
 </file>
@@ -744,58 +741,58 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>97.77777777777777</v>
+        <v>92.54032258064517</v>
       </c>
       <c r="C2">
-        <v>145</v>
+        <v>424</v>
       </c>
       <c r="D2">
-        <v>104.02</v>
+        <v>142.73</v>
       </c>
       <c r="E2">
-        <v>2.36</v>
+        <v>4.04</v>
       </c>
       <c r="F2">
-        <v>0.3024992265062308</v>
+        <v>1.427776505042221</v>
       </c>
       <c r="G2">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="H2">
-        <v>1.032156042731834</v>
+        <v>0.1901999389351708</v>
       </c>
       <c r="I2">
-        <v>100.6019989013672</v>
+        <v>139.0319976806641</v>
       </c>
       <c r="J2">
-        <v>95.8439998626709</v>
+        <v>131.1420009613037</v>
       </c>
       <c r="K2">
-        <v>99.09379974365234</v>
+        <v>121.1606005859375</v>
       </c>
       <c r="L2">
-        <v>72.39759994506836</v>
+        <v>92.27435031890869</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>9.444444444444443</v>
+        <v>15</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -804,49 +801,49 @@
         <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>41.64</v>
+        <v>43.9</v>
       </c>
       <c r="Y2">
-        <v>110.97</v>
+        <v>142.92</v>
       </c>
       <c r="Z2">
-        <v>28.54</v>
+        <v>14.07</v>
       </c>
       <c r="AA2">
-        <v>75.95</v>
+        <v>-1685.95</v>
       </c>
       <c r="AB2">
-        <v>336.8</v>
+        <v>2650</v>
       </c>
       <c r="AC2">
-        <v>701.59</v>
+        <v>233.33</v>
       </c>
       <c r="AD2">
-        <v>12.36</v>
+        <v>1.57</v>
       </c>
       <c r="AE2">
-        <v>62.9</v>
+        <v>-56.52</v>
       </c>
       <c r="AF2">
-        <v>136.64</v>
+        <v>53.33</v>
       </c>
       <c r="AG2">
-        <v>107.94</v>
+        <v>400</v>
       </c>
       <c r="AH2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AI2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AJ2" t="s">
         <v>71</v>
       </c>
       <c r="AK2">
-        <v>88.94324039847218</v>
+        <v>85.5127166964879</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -854,43 +851,43 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>99.79838709677419</v>
       </c>
       <c r="C3">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>353.6</v>
+        <v>284.08</v>
       </c>
       <c r="E3">
-        <v>4.39</v>
+        <v>3.75</v>
       </c>
       <c r="F3">
-        <v>2.532790133797933</v>
+        <v>1.094756247833982</v>
       </c>
       <c r="G3">
-        <v>3.65</v>
+        <v>3.87</v>
       </c>
       <c r="H3">
-        <v>2.600577712479805</v>
+        <v>2.228056427526282</v>
       </c>
       <c r="I3">
-        <v>342.5860046386719</v>
+        <v>284.6339965820313</v>
       </c>
       <c r="J3">
-        <v>287.4832473754883</v>
+        <v>282.9894989013672</v>
       </c>
       <c r="K3">
-        <v>236.6354992675781</v>
+        <v>242.3534655761719</v>
       </c>
       <c r="L3">
-        <v>159.5197748565674</v>
+        <v>139.673182888031</v>
       </c>
       <c r="M3">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -899,13 +896,13 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -917,46 +914,46 @@
         <v>1</v>
       </c>
       <c r="X3">
-        <v>54.21</v>
+        <v>23.37</v>
       </c>
       <c r="Y3">
-        <v>362</v>
+        <v>300.13</v>
       </c>
       <c r="Z3">
-        <v>56.31</v>
+        <v>764.24</v>
       </c>
       <c r="AA3">
-        <v>0.05</v>
+        <v>-13.71</v>
       </c>
       <c r="AB3">
-        <v>179.56</v>
+        <v>178.16</v>
       </c>
       <c r="AC3">
-        <v>1083.87</v>
+        <v>1392.54</v>
       </c>
       <c r="AD3">
-        <v>31.81</v>
+        <v>1.28</v>
       </c>
       <c r="AE3">
-        <v>529.58</v>
+        <v>-6.28</v>
       </c>
       <c r="AF3">
-        <v>-20.34</v>
+        <v>190.74</v>
       </c>
       <c r="AG3">
-        <v>-90.31999999999999</v>
+        <v>447.76</v>
       </c>
       <c r="AH3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AI3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AJ3" t="s">
         <v>72</v>
       </c>
       <c r="AK3">
-        <v>78.86760919417988</v>
+        <v>72.62998311826622</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -964,58 +961,58 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>96.96969696969697</v>
+        <v>97.98387096774194</v>
       </c>
       <c r="C4">
-        <v>199</v>
+        <v>48</v>
       </c>
       <c r="D4">
-        <v>64.45</v>
+        <v>269.44</v>
       </c>
       <c r="E4">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="F4">
-        <v>0.5991389038307431</v>
+        <v>0.02679473333859306</v>
       </c>
       <c r="G4">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="H4">
-        <v>0.6439328571506528</v>
+        <v>-0.1569904257877591</v>
       </c>
       <c r="I4">
-        <v>62.50199966430664</v>
+        <v>256.5440002441406</v>
       </c>
       <c r="J4">
-        <v>60.77650012969971</v>
+        <v>245.5004989624023</v>
       </c>
       <c r="K4">
-        <v>61.45900039672851</v>
+        <v>233.1493988037109</v>
       </c>
       <c r="L4">
-        <v>47.4155000114441</v>
+        <v>191.4530498123169</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>8.333333333333332</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -1024,49 +1021,49 @@
         <v>1</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>26.81</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="Y4">
-        <v>66.88</v>
+        <v>274.94</v>
       </c>
       <c r="Z4">
-        <v>12.59</v>
+        <v>278</v>
       </c>
       <c r="AA4">
-        <v>283.97</v>
+        <v>42.37</v>
       </c>
       <c r="AB4">
-        <v>126.09</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="AC4">
-        <v>597.92</v>
+        <v>1814.29</v>
       </c>
       <c r="AD4">
-        <v>14.67</v>
+        <v>7.81</v>
       </c>
       <c r="AE4">
-        <v>64.22</v>
+        <v>54.02</v>
       </c>
       <c r="AF4">
-        <v>129.21</v>
+        <v>-33.08</v>
       </c>
       <c r="AG4">
-        <v>85.42</v>
+        <v>1757.14</v>
       </c>
       <c r="AH4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AI4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="AJ4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AK4">
-        <v>74.65358364565799</v>
+        <v>58.10043131612499</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1074,58 +1071,58 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>98.38383838383838</v>
+        <v>98.38709677419355</v>
       </c>
       <c r="C5">
-        <v>200</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>161.7</v>
+        <v>31.73</v>
       </c>
       <c r="E5">
-        <v>2.11</v>
+        <v>4.26</v>
       </c>
       <c r="F5">
-        <v>0.02783285861316397</v>
+        <v>1.680412562234678</v>
       </c>
       <c r="G5">
-        <v>1.82</v>
+        <v>3.14</v>
       </c>
       <c r="H5">
-        <v>-0.2412160059744402</v>
+        <v>1.1261044003622</v>
       </c>
       <c r="I5">
-        <v>162.3759979248047</v>
+        <v>29.41999969482422</v>
       </c>
       <c r="J5">
-        <v>159.6769996643066</v>
+        <v>29.60749988555908</v>
       </c>
       <c r="K5">
-        <v>159.5009997558594</v>
+        <v>26.90439990997314</v>
       </c>
       <c r="L5">
-        <v>123.9185499954224</v>
+        <v>17.13369998693466</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="N5">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5">
-        <v>3.333333333333333</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -1137,46 +1134,46 @@
         <v>1</v>
       </c>
       <c r="X5">
-        <v>62.26</v>
+        <v>4.82</v>
       </c>
       <c r="Y5">
-        <v>168</v>
+        <v>32.49</v>
       </c>
       <c r="Z5">
-        <v>69.97</v>
+        <v>38.02</v>
       </c>
       <c r="AA5">
-        <v>6.13</v>
+        <v>-0.04</v>
       </c>
       <c r="AB5">
-        <v>432.98</v>
+        <v>180.39</v>
       </c>
       <c r="AC5">
-        <v>50.89</v>
+        <v>247.06</v>
       </c>
       <c r="AD5">
-        <v>5.47</v>
+        <v>4.6</v>
       </c>
       <c r="AE5">
-        <v>8.359999999999999</v>
+        <v>127.27</v>
       </c>
       <c r="AF5">
-        <v>30.02</v>
+        <v>633.33</v>
       </c>
       <c r="AG5">
-        <v>7.1</v>
+        <v>108.82</v>
       </c>
       <c r="AH5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK5">
-        <v>68.42286267536049</v>
+        <v>54.42181974931153</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1184,49 +1181,49 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>97.97979797979798</v>
+        <v>96.37096774193549</v>
       </c>
       <c r="C6">
-        <v>297</v>
+        <v>77</v>
       </c>
       <c r="D6">
-        <v>124.32</v>
+        <v>38.39</v>
       </c>
       <c r="E6">
-        <v>2.49</v>
+        <v>2.85</v>
       </c>
       <c r="F6">
-        <v>0.445325737810626</v>
+        <v>0.06124510477392845</v>
       </c>
       <c r="G6">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H6">
-        <v>0.1004203973369992</v>
+        <v>-0.4890855572618663</v>
       </c>
       <c r="I6">
-        <v>124.4739990234375</v>
+        <v>37.39199981689453</v>
       </c>
       <c r="J6">
-        <v>122.2774997711182</v>
+        <v>36.75100002288819</v>
       </c>
       <c r="K6">
-        <v>120.5690000915527</v>
+        <v>33.36980007171631</v>
       </c>
       <c r="L6">
-        <v>98.24295007705689</v>
+        <v>24.22335002422333</v>
       </c>
       <c r="M6">
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1235,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1247,46 +1244,46 @@
         <v>1</v>
       </c>
       <c r="X6">
-        <v>48.36</v>
+        <v>8.17</v>
       </c>
       <c r="Y6">
-        <v>127.65</v>
+        <v>39.43</v>
       </c>
       <c r="Z6">
-        <v>35.96</v>
+        <v>13.71</v>
       </c>
       <c r="AA6">
-        <v>6.56</v>
+        <v>33.89</v>
       </c>
       <c r="AB6">
-        <v>178.47</v>
+        <v>16.33</v>
       </c>
       <c r="AC6">
-        <v>126.94</v>
+        <v>800</v>
       </c>
       <c r="AD6">
-        <v>14.02</v>
+        <v>2.52</v>
       </c>
       <c r="AE6">
-        <v>10.32</v>
-      </c>
-      <c r="AF6">
-        <v>93.84999999999999</v>
+        <v>-46.15</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>52</v>
       </c>
       <c r="AG6">
-        <v>6.12</v>
+        <v>100</v>
       </c>
       <c r="AH6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AI6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AJ6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AK6">
-        <v>63.87062815302178</v>
+        <v>40.29892857224439</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1294,43 +1291,43 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>94.34343434343434</v>
+        <v>91.53225806451613</v>
       </c>
       <c r="C7">
-        <v>163</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>115.27</v>
+        <v>167.61</v>
       </c>
       <c r="E7">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="F7">
-        <v>-0.1919002357012895</v>
+        <v>-1.098584066882353</v>
       </c>
       <c r="G7">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="H7">
-        <v>-0.7070838286718576</v>
+        <v>-1.258942452951841</v>
       </c>
       <c r="I7">
-        <v>114.765998840332</v>
+        <v>167.1855987548828</v>
       </c>
       <c r="J7">
-        <v>105.0895000457764</v>
+        <v>162.0344985961914</v>
       </c>
       <c r="K7">
-        <v>99.10280029296875</v>
+        <v>160.5364895629883</v>
       </c>
       <c r="L7">
-        <v>76.20875011444092</v>
+        <v>150.8255795669556</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1354,49 +1351,49 @@
         <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>49.26</v>
+        <v>81.3</v>
       </c>
       <c r="Y7">
-        <v>117.15</v>
+        <v>177.61</v>
       </c>
       <c r="Z7">
-        <v>70.06</v>
+        <v>1660.71</v>
       </c>
       <c r="AA7">
-        <v>148.48</v>
+        <v>3033.7</v>
       </c>
       <c r="AB7">
-        <v>192.86</v>
+        <v>49.21</v>
       </c>
       <c r="AC7">
-        <v>59.65</v>
+        <v>182.51</v>
       </c>
       <c r="AD7">
-        <v>15.46</v>
+        <v>7.73</v>
       </c>
       <c r="AE7">
-        <v>-26.32</v>
+        <v>13.86</v>
       </c>
       <c r="AF7">
-        <v>118.58</v>
+        <v>20.29</v>
       </c>
       <c r="AG7">
-        <v>-0.88</v>
+        <v>106.29</v>
       </c>
       <c r="AH7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AI7" t="s">
         <v>67</v>
       </c>
       <c r="AJ7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AK7">
-        <v>57.46371996211623</v>
+        <v>39.29376020540442</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1404,49 +1401,49 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>91.11111111111111</v>
+        <v>92.94354838709677</v>
       </c>
       <c r="C8">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="D8">
-        <v>69.01000000000001</v>
+        <v>288.03</v>
       </c>
       <c r="E8">
-        <v>1.99</v>
+        <v>2.98</v>
       </c>
       <c r="F8">
-        <v>-0.104006997975508</v>
+        <v>0.2105300476603804</v>
       </c>
       <c r="G8">
-        <v>1.79</v>
+        <v>2.24</v>
       </c>
       <c r="H8">
-        <v>-0.2878027882441819</v>
+        <v>-0.232466592031874</v>
       </c>
       <c r="I8">
-        <v>68.84000091552734</v>
+        <v>291.9919982910156</v>
       </c>
       <c r="J8">
-        <v>67.61350040435791</v>
+        <v>295.901498413086</v>
       </c>
       <c r="K8">
-        <v>67.66179992675781</v>
+        <v>273.906598815918</v>
       </c>
       <c r="L8">
-        <v>54.74959991455078</v>
+        <v>215.4104494476318</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="N8">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1455,58 +1452,58 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>2.222222222222222</v>
+        <v>0</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>31.82</v>
+        <v>110.19</v>
       </c>
       <c r="Y8">
-        <v>70.68000000000001</v>
+        <v>317.6</v>
       </c>
       <c r="Z8">
-        <v>15.71</v>
+        <v>40.28</v>
       </c>
       <c r="AA8">
-        <v>3.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB8">
-        <v>44.08</v>
+        <v>15.42</v>
       </c>
       <c r="AC8">
-        <v>62</v>
+        <v>492</v>
       </c>
       <c r="AD8">
-        <v>3.02</v>
+        <v>15.49</v>
       </c>
       <c r="AE8">
-        <v>8</v>
+        <v>9.23</v>
       </c>
       <c r="AF8">
-        <v>-27.18</v>
+        <v>1.88</v>
       </c>
       <c r="AG8">
-        <v>106</v>
+        <v>432</v>
       </c>
       <c r="AH8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AI8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AJ8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AK8">
-        <v>40.5303969593606</v>
+        <v>36.44952406188037</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1514,46 +1511,46 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>92.72727272727272</v>
+        <v>95.36290322580645</v>
       </c>
       <c r="C9">
-        <v>343</v>
+        <v>456</v>
       </c>
       <c r="D9">
-        <v>361.59</v>
+        <v>502.64</v>
       </c>
       <c r="E9">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="F9">
-        <v>-0.642353079045919</v>
+        <v>-0.6507292382229972</v>
       </c>
       <c r="G9">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="H9">
-        <v>-0.7226127560951048</v>
+        <v>-0.9570377879753803</v>
       </c>
       <c r="I9">
-        <v>356.7859924316406</v>
+        <v>496.2140014648438</v>
       </c>
       <c r="J9">
-        <v>350.6019989013672</v>
+        <v>491.8099975585938</v>
       </c>
       <c r="K9">
-        <v>350.224799194336</v>
+        <v>481.1983984375</v>
       </c>
       <c r="L9">
-        <v>321.0636497497559</v>
+        <v>392.610650177002</v>
       </c>
       <c r="M9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1565,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1574,49 +1571,49 @@
         <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>173.36</v>
+        <v>168.65</v>
       </c>
       <c r="Y9">
-        <v>400.34</v>
+        <v>522.9</v>
       </c>
       <c r="Z9">
-        <v>116.89</v>
+        <v>43.35</v>
       </c>
       <c r="AA9">
-        <v>6.81</v>
+        <v>20.49</v>
       </c>
       <c r="AB9">
-        <v>26.82</v>
+        <v>8.6</v>
       </c>
       <c r="AC9">
-        <v>120.85</v>
+        <v>56.49</v>
       </c>
       <c r="AD9">
-        <v>11.86</v>
+        <v>27.65</v>
       </c>
       <c r="AE9">
-        <v>46.67</v>
+        <v>19.88</v>
       </c>
       <c r="AF9">
-        <v>62.5</v>
+        <v>-2.29</v>
       </c>
       <c r="AG9">
-        <v>-7.34</v>
+        <v>33.59</v>
       </c>
       <c r="AH9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AI9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AK9">
-        <v>38.21447775451873</v>
+        <v>17.9248400877412</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1624,43 +1621,43 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>90.30303030303031</v>
+        <v>97.78225806451613</v>
       </c>
       <c r="C10">
-        <v>309</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>248.2</v>
+        <v>13.59</v>
       </c>
       <c r="E10">
-        <v>3.31</v>
+        <v>1.97</v>
       </c>
       <c r="F10">
-        <v>1.346231424499885</v>
+        <v>-0.9492991239959014</v>
       </c>
       <c r="G10">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="H10">
-        <v>0.3954700183786967</v>
+        <v>-0.4136093910177507</v>
       </c>
       <c r="I10">
-        <v>247.09599609375</v>
+        <v>13.51590023040771</v>
       </c>
       <c r="J10">
-        <v>231.1889976501465</v>
+        <v>13.378600025177</v>
       </c>
       <c r="K10">
-        <v>217.9719989013672</v>
+        <v>13.27696500778198</v>
       </c>
       <c r="L10">
-        <v>183.1102997207641</v>
+        <v>11.64810250759125</v>
       </c>
       <c r="M10">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1687,46 +1684,46 @@
         <v>1</v>
       </c>
       <c r="X10">
-        <v>114.38</v>
+        <v>4.52</v>
       </c>
       <c r="Y10">
-        <v>254.45</v>
+        <v>14.73</v>
       </c>
       <c r="Z10">
-        <v>68.76000000000001</v>
+        <v>315.86</v>
       </c>
       <c r="AA10">
-        <v>5.14</v>
+        <v>2247.37</v>
       </c>
       <c r="AB10">
-        <v>25.08</v>
+        <v>12.36</v>
       </c>
       <c r="AC10">
-        <v>124.37</v>
+        <v>37.76</v>
       </c>
       <c r="AD10">
-        <v>92.95999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AE10">
-        <v>4.99</v>
+        <v>116</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>-32.98</v>
       </c>
       <c r="AG10">
-        <v>113.71</v>
+        <v>-4.85</v>
       </c>
       <c r="AH10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="s">
         <v>66</v>
       </c>
       <c r="AJ10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AK10">
-        <v>37.61483381661891</v>
+        <v>16.94438455476509</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1734,109 +1731,109 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>99.19191919191918</v>
+        <v>94.75806451612904</v>
       </c>
       <c r="C11">
-        <v>321</v>
+        <v>438</v>
       </c>
       <c r="D11">
-        <v>419.36</v>
+        <v>272.92</v>
       </c>
       <c r="E11">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="F11">
-        <v>-0.4226199847314656</v>
+        <v>-1.018199866866572</v>
       </c>
       <c r="G11">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="H11">
-        <v>0.2867675264159663</v>
+        <v>-0.6551331229989196</v>
       </c>
       <c r="I11">
-        <v>430.6539978027344</v>
+        <v>268.3100036621094</v>
       </c>
       <c r="J11">
-        <v>434.955500793457</v>
+        <v>264.3415016174316</v>
       </c>
       <c r="K11">
-        <v>388.0169989013672</v>
+        <v>251.7226010131836</v>
       </c>
       <c r="L11">
-        <v>300.8374489593506</v>
+        <v>211.9188001251221</v>
       </c>
       <c r="M11">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="P11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>17.22222222222222</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
       </c>
       <c r="V11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="b">
         <v>0</v>
       </c>
       <c r="X11">
-        <v>151.5</v>
+        <v>104.9</v>
       </c>
       <c r="Y11">
-        <v>457</v>
+        <v>280.11</v>
       </c>
       <c r="Z11">
-        <v>26.61</v>
+        <v>33.3</v>
       </c>
       <c r="AA11">
-        <v>73.06999999999999</v>
+        <v>25.71</v>
       </c>
       <c r="AB11">
-        <v>40.71</v>
+        <v>3.77</v>
       </c>
       <c r="AC11">
-        <v>10.75</v>
+        <v>89.86</v>
       </c>
       <c r="AD11">
-        <v>7.72</v>
+        <v>4</v>
       </c>
       <c r="AE11">
-        <v>-13.81</v>
+        <v>-21.56</v>
       </c>
       <c r="AF11">
-        <v>18.32</v>
+        <v>128.77</v>
       </c>
       <c r="AG11">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AH11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AI11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AJ11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK11">
-        <v>35.26584994198909</v>
+        <v>15.7667341600016</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1844,46 +1841,46 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>93.73737373737374</v>
+        <v>94.95967741935483</v>
       </c>
       <c r="C12">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="D12">
-        <v>261.05</v>
+        <v>126.12</v>
       </c>
       <c r="E12">
-        <v>0.8100000000000001</v>
+        <v>3.23</v>
       </c>
       <c r="F12">
-        <v>-1.400432254430783</v>
+        <v>0.497616476288173</v>
       </c>
       <c r="G12">
-        <v>1.23</v>
+        <v>2.46</v>
       </c>
       <c r="H12">
-        <v>-1.157422723946028</v>
+        <v>0.0996285394422325</v>
       </c>
       <c r="I12">
-        <v>259.8699951171875</v>
+        <v>122.2740005493164</v>
       </c>
       <c r="J12">
-        <v>253.8854988098145</v>
+        <v>131.3595008850098</v>
       </c>
       <c r="K12">
-        <v>241.0210000610352</v>
+        <v>122.8778002929687</v>
       </c>
       <c r="L12">
-        <v>198.7453507232666</v>
+        <v>92.046100025177</v>
       </c>
       <c r="M12">
-        <v>1.02</v>
+        <v>0.93</v>
       </c>
       <c r="N12">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -1895,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>0.5555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
@@ -1907,46 +1904,46 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>123.79</v>
+        <v>42.87</v>
       </c>
       <c r="Y12">
-        <v>263.46</v>
+        <v>143.4</v>
       </c>
       <c r="Z12">
-        <v>104.33</v>
+        <v>21.94</v>
       </c>
       <c r="AA12">
-        <v>5.69</v>
+        <v>63.42</v>
       </c>
       <c r="AB12">
-        <v>39.86</v>
+        <v>24.21</v>
       </c>
       <c r="AC12">
-        <v>24.26</v>
+        <v>11.32</v>
       </c>
       <c r="AD12">
-        <v>14.02</v>
+        <v>8.9</v>
       </c>
       <c r="AE12">
-        <v>52.73</v>
+        <v>-11.94</v>
       </c>
       <c r="AF12">
-        <v>36.14</v>
+        <v>17.54</v>
       </c>
       <c r="AG12">
-        <v>-40.24</v>
+        <v>7.55</v>
       </c>
       <c r="AH12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AI12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AJ12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AK12">
-        <v>31.24656273343743</v>
+        <v>14.48800357213934</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -1954,49 +1951,49 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>94.74747474747474</v>
+        <v>95.76612903225806</v>
       </c>
       <c r="C13">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="D13">
-        <v>139.93</v>
+        <v>291.35</v>
       </c>
       <c r="E13">
-        <v>1.93</v>
+        <v>1.08</v>
       </c>
       <c r="F13">
-        <v>-0.1699269262698441</v>
+        <v>-1.971326809910843</v>
       </c>
       <c r="G13">
-        <v>2.37</v>
+        <v>1.48</v>
       </c>
       <c r="H13">
-        <v>0.6128750023041584</v>
+        <v>-1.379704318942426</v>
       </c>
       <c r="I13">
-        <v>137.6039978027344</v>
+        <v>293.0599975585938</v>
       </c>
       <c r="J13">
-        <v>135.4789970397949</v>
+        <v>298.3189987182617</v>
       </c>
       <c r="K13">
-        <v>136.2657992553711</v>
+        <v>284.8601995849609</v>
       </c>
       <c r="L13">
-        <v>111.0135500335693</v>
+        <v>259.8830000305176</v>
       </c>
       <c r="M13">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="N13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -2005,49 +2002,49 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>4.444444444444444</v>
       </c>
       <c r="U13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="b">
         <v>1</v>
       </c>
       <c r="X13">
-        <v>54.15</v>
+        <v>124.53</v>
       </c>
       <c r="Y13">
-        <v>146</v>
+        <v>312.12</v>
       </c>
       <c r="Z13">
-        <v>123.02</v>
+        <v>20.84</v>
       </c>
       <c r="AA13">
-        <v>39.78</v>
+        <v>26.94</v>
       </c>
       <c r="AB13">
-        <v>18.63</v>
+        <v>6.3</v>
       </c>
       <c r="AC13">
-        <v>57.61</v>
+        <v>29.07</v>
       </c>
       <c r="AD13">
-        <v>11.09</v>
+        <v>4.79</v>
       </c>
       <c r="AE13">
-        <v>17.89</v>
+        <v>-10.48</v>
       </c>
       <c r="AF13">
-        <v>-0.8100000000000001</v>
+        <v>22.77</v>
       </c>
       <c r="AG13">
-        <v>34.78</v>
+        <v>17.44</v>
       </c>
       <c r="AH13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AI13" t="s">
         <v>70</v>
@@ -2056,7 +2053,7 @@
         <v>80</v>
       </c>
       <c r="AK13">
-        <v>28.12736094322606</v>
+        <v>12.8800004969981</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2064,43 +2061,43 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>94.14141414141413</v>
+        <v>97.17741935483872</v>
       </c>
       <c r="C14">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="D14">
-        <v>264.73</v>
+        <v>359.51</v>
       </c>
       <c r="E14">
-        <v>0.79</v>
+        <v>2.88</v>
       </c>
       <c r="F14">
-        <v>-1.422405563862229</v>
+        <v>0.09569547620926333</v>
       </c>
       <c r="G14">
-        <v>1.08</v>
+        <v>2.64</v>
       </c>
       <c r="H14">
-        <v>-1.390356635294736</v>
+        <v>0.3713427379210475</v>
       </c>
       <c r="I14">
-        <v>263.5980041503906</v>
+        <v>367.1260009765625</v>
       </c>
       <c r="J14">
-        <v>257.6009994506836</v>
+        <v>379.9045028686523</v>
       </c>
       <c r="K14">
-        <v>244.1131988525391</v>
+        <v>354.2202020263672</v>
       </c>
       <c r="L14">
-        <v>189.3649501419067</v>
+        <v>281.9550509643555</v>
       </c>
       <c r="M14">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="N14">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2118,55 +2115,55 @@
         <v>0</v>
       </c>
       <c r="U14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>115.86</v>
+        <v>130.12</v>
       </c>
       <c r="Y14">
-        <v>265.35</v>
+        <v>406.75</v>
       </c>
       <c r="Z14">
-        <v>16.27</v>
+        <v>17.22</v>
       </c>
       <c r="AA14">
-        <v>9.279999999999999</v>
+        <v>55.5</v>
       </c>
       <c r="AB14">
-        <v>4.7</v>
+        <v>10.54</v>
       </c>
       <c r="AC14">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="AD14">
-        <v>18.41</v>
+        <v>4.44</v>
       </c>
       <c r="AE14">
-        <v>38.81</v>
+        <v>-22.58</v>
       </c>
       <c r="AF14">
-        <v>605.26</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="AG14">
-        <v>-69.34999999999999</v>
+        <v>-16.25</v>
       </c>
       <c r="AH14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AI14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AJ14" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AK14">
-        <v>21.96085173153241</v>
+        <v>11.40195921489027</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2174,46 +2171,46 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>91.91919191919192</v>
+        <v>96.57258064516128</v>
       </c>
       <c r="C15">
-        <v>483</v>
+        <v>260</v>
       </c>
       <c r="D15">
-        <v>552.48</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E15">
-        <v>1.51</v>
+        <v>3.09</v>
       </c>
       <c r="F15">
-        <v>-0.6313664243301963</v>
+        <v>0.336848076256609</v>
       </c>
       <c r="G15">
-        <v>1.54</v>
+        <v>3.39</v>
       </c>
       <c r="H15">
-        <v>-0.676025973825363</v>
+        <v>1.503485231582776</v>
       </c>
       <c r="I15">
-        <v>546.3619873046875</v>
+        <v>98.10599975585937</v>
       </c>
       <c r="J15">
-        <v>537.4154953002929</v>
+        <v>102.1194999694824</v>
       </c>
       <c r="K15">
-        <v>519.569599609375</v>
+        <v>97.36460006713867</v>
       </c>
       <c r="L15">
-        <v>444.7654495239258</v>
+        <v>72.33219993591308</v>
       </c>
       <c r="M15">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="N15">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="P15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2225,58 +2222,58 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>0.5555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
       </c>
       <c r="V15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="b">
         <v>1</v>
       </c>
       <c r="X15">
-        <v>246.83</v>
+        <v>28.47</v>
       </c>
       <c r="Y15">
-        <v>554.22</v>
+        <v>112.5</v>
       </c>
       <c r="Z15">
-        <v>26.18</v>
+        <v>7.07</v>
       </c>
       <c r="AA15">
-        <v>-15.19</v>
+        <v>0.7</v>
       </c>
       <c r="AB15">
-        <v>4.88</v>
+        <v>457.63</v>
       </c>
       <c r="AC15">
-        <v>127.81</v>
+        <v>360.71</v>
       </c>
       <c r="AD15">
-        <v>9.460000000000001</v>
+        <v>2.87</v>
       </c>
       <c r="AE15">
-        <v>14.52</v>
+        <v>317.14</v>
       </c>
       <c r="AF15">
-        <v>70.64</v>
+        <v>-59.3</v>
       </c>
       <c r="AG15">
-        <v>16.58</v>
+        <v>253.57</v>
       </c>
       <c r="AH15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AJ15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK15">
-        <v>19.23666259894658</v>
+        <v>63.26859914016083</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2284,46 +2281,46 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>90.90909090909091</v>
+        <v>92.13709677419355</v>
       </c>
       <c r="C16">
-        <v>49</v>
+        <v>267</v>
       </c>
       <c r="D16">
-        <v>95.98</v>
+        <v>52.79</v>
       </c>
       <c r="E16">
-        <v>1.84</v>
+        <v>3.02</v>
       </c>
       <c r="F16">
-        <v>-0.268806818711348</v>
+        <v>0.2564638762408273</v>
       </c>
       <c r="G16">
-        <v>1.66</v>
+        <v>2.41</v>
       </c>
       <c r="H16">
-        <v>-0.4896788447463963</v>
+        <v>0.02415237319811756</v>
       </c>
       <c r="I16">
-        <v>96.27000122070312</v>
+        <v>51.81766662597656</v>
       </c>
       <c r="J16">
-        <v>93.06800003051758</v>
+        <v>52.32883319854736</v>
       </c>
       <c r="K16">
-        <v>91.18919998168946</v>
+        <v>49.73540008544922</v>
       </c>
       <c r="L16">
-        <v>76.31609996795655</v>
+        <v>38.45240820884705</v>
       </c>
       <c r="M16">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="N16">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2335,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>1.111111111111111</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
@@ -2347,46 +2344,46 @@
         <v>1</v>
       </c>
       <c r="X16">
-        <v>45.86</v>
+        <v>13.12</v>
       </c>
       <c r="Y16">
-        <v>97.20999999999999</v>
+        <v>56.05</v>
       </c>
       <c r="Z16">
-        <v>168.8</v>
+        <v>8.15</v>
       </c>
       <c r="AA16">
-        <v>16.45</v>
+        <v>106.56</v>
       </c>
       <c r="AB16">
-        <v>4.94</v>
+        <v>23.7</v>
       </c>
       <c r="AC16">
-        <v>11.9</v>
+        <v>1875.23</v>
       </c>
       <c r="AD16">
-        <v>3.5</v>
+        <v>16.81</v>
       </c>
       <c r="AE16">
-        <v>-15.32</v>
+        <v>151.12</v>
       </c>
       <c r="AF16">
-        <v>18.72</v>
+        <v>1391.86</v>
       </c>
       <c r="AG16">
-        <v>11.31</v>
+        <v>-160.89</v>
       </c>
       <c r="AH16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AI16" t="s">
         <v>67</v>
       </c>
       <c r="AJ16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK16">
-        <v>1.890898971765676</v>
+        <v>50.42126644778009</v>
       </c>
     </row>
   </sheetData>
